--- a/光伏配储项目/电价数据/2026/富莲站.xlsx
+++ b/光伏配储项目/电价数据/2026/富莲站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.60505</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8110499999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.68101</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6077899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5932999999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5945499999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46948</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42715</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51742</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19904</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22016</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27036</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21466</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17547</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20054</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25258</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06214</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15966</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24287</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24581</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.9042</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22302</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.51985</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5355</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.52678</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6064299999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60793</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72622</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21649</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.79995</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65459</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93571</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.2772</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39437</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14507</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24803</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.35179</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.51696</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.51515</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75552</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.80729</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.31526</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12192</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86573</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79361</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75358</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70047</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74568</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86281</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.90367</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48926</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49707</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46232</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7008300000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55706</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.65995</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50958</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58166</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85666</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07261</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58335</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93601</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8901699999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5598099999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.84111</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.2496</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05733</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40928</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5868300000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54613</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86049</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60533</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7718200000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8418600000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.21373</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15862</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26385</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16807</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32686</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10824</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15278</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.71156</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04375</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8939400000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05461</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.96423</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.0753</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87975</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81414</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83438</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44096</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48274</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48021</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44164</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46735</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25164</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15975</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.54557</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48749</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5761000000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.58326</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6652100000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.6312000000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89678</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.58749</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.70105</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77803</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8656900000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52316</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7779700000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72163</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64476</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63678</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.5856</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5033299999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5113799999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5774900000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6114299999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57977</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.60121</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23516</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6102799999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.73933</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51087</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5776399999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71949</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71915</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.8633999999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59826</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.55183</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6015900000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7302799999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5627300000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.87461</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6988799999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51462</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34162</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51385</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46522</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46913</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6406799999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.50563</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.49004</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.02748</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49082</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49443</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6553600000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48285</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5338200000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6619400000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51844</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.71684</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55957</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.52342</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50201</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.48224</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30975</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24441</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26565</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14563</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24689</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23641</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18845</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24634</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25597</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22362</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08574</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18074</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26404</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3301</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21192</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09519</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22189</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24219</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27418</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23072</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25514</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20892</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19452</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19652</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.03639</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06307</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06128</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32327</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30133</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78496</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87115</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.7116699999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5932999999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44637</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50259</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56002</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65167</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8696200000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46094</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49359</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6958300000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83412</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.49018</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57736</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33498</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90462</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23768</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19449</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26323</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24847</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40452</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38455</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08555</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65384</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7427999999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6070599999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46428</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22869</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.05954</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24471</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14525</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02931</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2463</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48425</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.66759</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27339</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22326</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23548</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23111</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23807</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21359</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27358</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.09311</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22461</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09412000000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24955</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22078</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15767</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22208</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23722</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.2385</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22217</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24237</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22049</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23761</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24132</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22666</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42613</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30693</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23668</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.42058</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32614</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22367</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.47249</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.74887</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.55498</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5346799999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.50331</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5724900000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.49076</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6689299999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.51176</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.8435199999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.58228</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.54687</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5124099999999999</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6764600000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.50745</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.51918</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.5395700000000001</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.56443</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45867</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6989</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.51624</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49081</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47252</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7506699999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46914</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49061</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.15426</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24848</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25395</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24609</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24317</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21882</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26743</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25818</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22486</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23109</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33091</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63985</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.85003</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31474</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.48925</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.49591</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6394500000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6997100000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65723</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7334700000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.85009</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.69368</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5431699999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45408</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.53984</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33149</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47892</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47369</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45807</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.50558</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6161</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.62152</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6882200000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.87158</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.46424</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.51354</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6010599999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.44566</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5214500000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.49944</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.53101</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7546799999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6067899999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65379</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44014</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37403</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.14029</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.5412400000000001</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.16779</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.46347</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46483</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44399</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.47073</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23374</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25346</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26425</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23585</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.14009</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.13079</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.12982</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.12411</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22214</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23214</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.11965</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23571</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.11914</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.10347</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21227</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11435</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24755</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01664</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18847</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27153</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28168</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25511</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26827</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24563</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23073</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22972</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15087</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.10775</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25082</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13598</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.10142</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.10996</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10995</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.10818</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.10818</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10924</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23762</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.10818</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10834</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10149</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11265</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07252</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11569</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14186</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01597</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00086</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27461</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03843</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02208</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03635</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26448</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11108</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29968</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.52922</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.47475</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.21087</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23921</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23572</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11518</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23113</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2166</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11901</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08133</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09848999999999999</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10869</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.12295</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08816</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.13419</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.14093</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.15328</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10831</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86774</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85885</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10734</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16183</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.12566</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28447</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06666</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47341</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.09092</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.66111</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5587000000000001</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.07751</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97342</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.56751</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7251599999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.61398</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83021</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82843</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8327</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93041</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6100099999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5640700000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.46887</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48216</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23819</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25371</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.23093</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23439</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11546</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24637</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25768</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.49416</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32325</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.71116</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.4621499999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46162</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47945</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.54298</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.44674</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46972</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.85199</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.14885</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48991</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.57628</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.05658</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8884500000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.54238</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64891</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49174</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.46701</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22421</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34111</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.44576</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50466</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5951900000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.27447</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.04289</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6541699999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.88758</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.65311</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.58377</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.80938</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74618</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98891</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89136</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.80308</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7277899999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34556</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.44979</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.79913</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.48707</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21749</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.5829500000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44806</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.80452</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.49625</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.49299</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5364500000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.67547</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44909</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5248200000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48436</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6627000000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35149</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.91631</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.47788</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52885</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49511</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.50498</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5089399999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42272</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.51029</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.48823</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.47015</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.46389</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35206</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14314</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12087</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14759</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19215</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15193</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15409</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19597</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14078</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5032</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43621</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.55261</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37925</v>
       </c>
     </row>
   </sheetData>
